--- a/r4-ELGA-e-Medikation-main/StructureDefinition-MyPatient.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-MyPatient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-30T16:45:16+00:00</t>
+    <t>2026-01-13T12:36:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
